--- a/Final_Project/Control.xlsx
+++ b/Final_Project/Control.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\林佳葦\Desktop\iclab\Final_Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\學習\碩一\一上\ICLAB\ICLAB2025\Final_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F52E97D-9A67-46E4-B819-E085F7AEE46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E53A4C5-0E38-4A1D-8E02-EDBFA655290C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26445" yWindow="2910" windowWidth="25095" windowHeight="12330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6528" yWindow="1296" windowWidth="23040" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -540,12 +540,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O25"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="12" width="10.7109375" customWidth="1"/>
+    <col min="1" max="12" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -561,7 +561,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -602,7 +602,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>-2</v>
       </c>
@@ -643,7 +643,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>24</v>
@@ -682,7 +682,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
@@ -723,7 +723,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
@@ -764,7 +764,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -779,7 +779,7 @@
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2">
@@ -810,7 +810,7 @@
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -826,7 +826,7 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>126</v>
       </c>
@@ -843,27 +843,27 @@
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O11">
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O12">
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O13" s="1">
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O14">
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -889,7 +889,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
         <v>28</v>
       </c>
@@ -902,7 +902,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>30</v>
       </c>
@@ -928,7 +928,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -954,7 +954,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>32</v>
       </c>
@@ -980,7 +980,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -1006,12 +1006,12 @@
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O21">
         <v>122</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>33</v>
       </c>
